--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="C2" t="n">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="D2" t="n">
-        <v>0.028017</v>
+        <v>0.019404</v>
       </c>
       <c r="E2" t="n">
-        <v>0.180364</v>
+        <v>0.158605</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07244399999999999</v>
+        <v>0.061875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.766024</v>
+        <v>0.626995</v>
       </c>
       <c r="H2" t="n">
-        <v>0.865683</v>
+        <v>0.770159</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="C3" t="n">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="D3" t="n">
-        <v>0.020961</v>
+        <v>0.011674</v>
       </c>
       <c r="E3" t="n">
-        <v>0.105824</v>
+        <v>0.082399</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05608</v>
+        <v>0.047935</v>
       </c>
       <c r="G3" t="n">
-        <v>0.337412</v>
+        <v>0.259082</v>
       </c>
       <c r="H3" t="n">
-        <v>0.526157</v>
+        <v>0.305454</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="C4" t="n">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="D4" t="n">
-        <v>0.022754</v>
+        <v>0.01267</v>
       </c>
       <c r="E4" t="n">
-        <v>0.114876</v>
+        <v>0.089425</v>
       </c>
       <c r="F4" t="n">
-        <v>0.060877</v>
+        <v>0.052023</v>
       </c>
       <c r="G4" t="n">
-        <v>0.366273</v>
+        <v>0.281174</v>
       </c>
       <c r="H4" t="n">
-        <v>0.571163</v>
+        <v>0.3315</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001793</v>
+        <v>0.0009959999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009051999999999999</v>
+        <v>0.007026</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004797</v>
+        <v>0.004088</v>
       </c>
       <c r="G5" t="n">
-        <v>0.028861</v>
+        <v>0.022092</v>
       </c>
       <c r="H5" t="n">
-        <v>0.045006</v>
+        <v>0.026046</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>752</v>
+        <v>695</v>
       </c>
       <c r="C2" t="n">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="D2" t="n">
-        <v>0.019404</v>
+        <v>0.02126</v>
       </c>
       <c r="E2" t="n">
-        <v>0.158605</v>
+        <v>0.162249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.061875</v>
+        <v>0.063027</v>
       </c>
       <c r="G2" t="n">
-        <v>0.626995</v>
+        <v>0.63491</v>
       </c>
       <c r="H2" t="n">
-        <v>0.770159</v>
+        <v>0.774709</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>752</v>
+        <v>695</v>
       </c>
       <c r="C3" t="n">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="D3" t="n">
-        <v>0.011674</v>
+        <v>0.012928</v>
       </c>
       <c r="E3" t="n">
-        <v>0.082399</v>
+        <v>0.08352999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.047935</v>
+        <v>0.050011</v>
       </c>
       <c r="G3" t="n">
-        <v>0.259082</v>
+        <v>0.243554</v>
       </c>
       <c r="H3" t="n">
-        <v>0.305454</v>
+        <v>0.310539</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>752</v>
+        <v>695</v>
       </c>
       <c r="C4" t="n">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01267</v>
+        <v>0.014003</v>
       </c>
       <c r="E4" t="n">
-        <v>0.089425</v>
+        <v>0.09048100000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.052023</v>
+        <v>0.054172</v>
       </c>
       <c r="G4" t="n">
-        <v>0.281174</v>
+        <v>0.263819</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3315</v>
+        <v>0.336378</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.0009959999999999999</v>
+        <v>0.001075</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007026</v>
+        <v>0.006951</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004088</v>
+        <v>0.004161</v>
       </c>
       <c r="G5" t="n">
-        <v>0.022092</v>
+        <v>0.020265</v>
       </c>
       <c r="H5" t="n">
-        <v>0.026046</v>
+        <v>0.025839</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="C2" t="n">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02126</v>
+        <v>0.023535</v>
       </c>
       <c r="E2" t="n">
-        <v>0.162249</v>
+        <v>0.165835</v>
       </c>
       <c r="F2" t="n">
-        <v>0.063027</v>
+        <v>0.066471</v>
       </c>
       <c r="G2" t="n">
-        <v>0.63491</v>
+        <v>0.654959</v>
       </c>
       <c r="H2" t="n">
-        <v>0.774709</v>
+        <v>0.744555</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="C3" t="n">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D3" t="n">
-        <v>0.012928</v>
+        <v>0.014648</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08352999999999999</v>
+        <v>0.08809599999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.050011</v>
+        <v>0.050886</v>
       </c>
       <c r="G3" t="n">
-        <v>0.243554</v>
+        <v>0.300346</v>
       </c>
       <c r="H3" t="n">
-        <v>0.310539</v>
+        <v>0.343367</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="C4" t="n">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014003</v>
+        <v>0.015825</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09048100000000001</v>
+        <v>0.095176</v>
       </c>
       <c r="F4" t="n">
-        <v>0.054172</v>
+        <v>0.054976</v>
       </c>
       <c r="G4" t="n">
-        <v>0.263819</v>
+        <v>0.324485</v>
       </c>
       <c r="H4" t="n">
-        <v>0.336378</v>
+        <v>0.370963</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001075</v>
+        <v>0.001177</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006951</v>
+        <v>0.00708</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004161</v>
+        <v>0.00409</v>
       </c>
       <c r="G5" t="n">
-        <v>0.020265</v>
+        <v>0.024139</v>
       </c>
       <c r="H5" t="n">
-        <v>0.025839</v>
+        <v>0.027596</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="C2" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023535</v>
+        <v>0.023657</v>
       </c>
       <c r="E2" t="n">
-        <v>0.165835</v>
+        <v>0.166206</v>
       </c>
       <c r="F2" t="n">
-        <v>0.066471</v>
+        <v>0.06464300000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.654959</v>
+        <v>0.67306</v>
       </c>
       <c r="H2" t="n">
-        <v>0.744555</v>
+        <v>0.742665</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="C3" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D3" t="n">
-        <v>0.014648</v>
+        <v>0.014514</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08809599999999999</v>
+        <v>0.08697199999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.050886</v>
+        <v>0.049558</v>
       </c>
       <c r="G3" t="n">
-        <v>0.300346</v>
+        <v>0.297544</v>
       </c>
       <c r="H3" t="n">
-        <v>0.343367</v>
+        <v>0.341237</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="C4" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D4" t="n">
-        <v>0.015825</v>
+        <v>0.01569</v>
       </c>
       <c r="E4" t="n">
-        <v>0.095176</v>
+        <v>0.09402199999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.054976</v>
+        <v>0.053576</v>
       </c>
       <c r="G4" t="n">
-        <v>0.324485</v>
+        <v>0.321665</v>
       </c>
       <c r="H4" t="n">
-        <v>0.370963</v>
+        <v>0.3689</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001177</v>
+        <v>0.001176</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00708</v>
+        <v>0.00705</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00409</v>
+        <v>0.004018</v>
       </c>
       <c r="G5" t="n">
-        <v>0.024139</v>
+        <v>0.024121</v>
       </c>
       <c r="H5" t="n">
-        <v>0.027596</v>
+        <v>0.027663</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="C2" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023657</v>
+        <v>0.027268</v>
       </c>
       <c r="E2" t="n">
-        <v>0.166206</v>
+        <v>0.165768</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06464300000000001</v>
+        <v>0.061748</v>
       </c>
       <c r="G2" t="n">
-        <v>0.67306</v>
+        <v>0.673009</v>
       </c>
       <c r="H2" t="n">
-        <v>0.742665</v>
+        <v>0.741044</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="C3" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D3" t="n">
-        <v>0.014514</v>
+        <v>0.013244</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08697199999999999</v>
+        <v>0.06780899999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.049558</v>
+        <v>0.045898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.297544</v>
+        <v>0.226183</v>
       </c>
       <c r="H3" t="n">
-        <v>0.341237</v>
+        <v>0.280208</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="C4" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01569</v>
+        <v>0.014283</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09402199999999999</v>
+        <v>0.073133</v>
       </c>
       <c r="F4" t="n">
-        <v>0.053576</v>
+        <v>0.049502</v>
       </c>
       <c r="G4" t="n">
-        <v>0.321665</v>
+        <v>0.243942</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3689</v>
+        <v>0.302208</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001176</v>
+        <v>0.001039</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00705</v>
+        <v>0.005324</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004018</v>
+        <v>0.003604</v>
       </c>
       <c r="G5" t="n">
-        <v>0.024121</v>
+        <v>0.017759</v>
       </c>
       <c r="H5" t="n">
-        <v>0.027663</v>
+        <v>0.022</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C2" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D2" t="n">
-        <v>0.027268</v>
+        <v>0.024576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.165768</v>
+        <v>0.135997</v>
       </c>
       <c r="F2" t="n">
-        <v>0.061748</v>
+        <v>0.061784</v>
       </c>
       <c r="G2" t="n">
-        <v>0.673009</v>
+        <v>0.672434</v>
       </c>
       <c r="H2" t="n">
-        <v>0.741044</v>
+        <v>0.711338</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C3" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D3" t="n">
-        <v>0.013244</v>
+        <v>0.01338</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06780899999999999</v>
+        <v>0.064291</v>
       </c>
       <c r="F3" t="n">
-        <v>0.045898</v>
+        <v>0.045557</v>
       </c>
       <c r="G3" t="n">
-        <v>0.226183</v>
+        <v>0.210785</v>
       </c>
       <c r="H3" t="n">
-        <v>0.280208</v>
+        <v>0.253831</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C4" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014283</v>
+        <v>0.014455</v>
       </c>
       <c r="E4" t="n">
-        <v>0.073133</v>
+        <v>0.069456</v>
       </c>
       <c r="F4" t="n">
-        <v>0.049502</v>
+        <v>0.049217</v>
       </c>
       <c r="G4" t="n">
-        <v>0.243942</v>
+        <v>0.227718</v>
       </c>
       <c r="H4" t="n">
-        <v>0.302208</v>
+        <v>0.274223</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001039</v>
+        <v>0.001075</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005324</v>
+        <v>0.005165</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003604</v>
+        <v>0.00366</v>
       </c>
       <c r="G5" t="n">
-        <v>0.017759</v>
+        <v>0.016933</v>
       </c>
       <c r="H5" t="n">
-        <v>0.022</v>
+        <v>0.020392</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C2" t="n">
         <v>376</v>
       </c>
       <c r="D2" t="n">
-        <v>0.024576</v>
+        <v>0.02454</v>
       </c>
       <c r="E2" t="n">
-        <v>0.135997</v>
+        <v>0.135901</v>
       </c>
       <c r="F2" t="n">
         <v>0.061784</v>
@@ -493,16 +493,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C3" t="n">
         <v>376</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01338</v>
+        <v>0.013361</v>
       </c>
       <c r="E3" t="n">
-        <v>0.064291</v>
+        <v>0.064246</v>
       </c>
       <c r="F3" t="n">
         <v>0.045557</v>
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C4" t="n">
         <v>376</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014455</v>
+        <v>0.014434</v>
       </c>
       <c r="E4" t="n">
-        <v>0.069456</v>
+        <v>0.069408</v>
       </c>
       <c r="F4" t="n">
         <v>0.049217</v>
@@ -551,10 +551,10 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001075</v>
+        <v>0.001073</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005165</v>
+        <v>0.005162</v>
       </c>
       <c r="F5" t="n">
         <v>0.00366</v>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -499,19 +499,19 @@
         <v>376</v>
       </c>
       <c r="D3" t="n">
-        <v>0.013361</v>
+        <v>0.013417</v>
       </c>
       <c r="E3" t="n">
-        <v>0.064246</v>
+        <v>0.064624</v>
       </c>
       <c r="F3" t="n">
-        <v>0.045557</v>
+        <v>0.045842</v>
       </c>
       <c r="G3" t="n">
-        <v>0.210785</v>
+        <v>0.211738</v>
       </c>
       <c r="H3" t="n">
-        <v>0.253831</v>
+        <v>0.25523</v>
       </c>
     </row>
     <row r="4">
@@ -527,19 +527,19 @@
         <v>376</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014434</v>
+        <v>0.014498</v>
       </c>
       <c r="E4" t="n">
-        <v>0.069408</v>
+        <v>0.06983</v>
       </c>
       <c r="F4" t="n">
-        <v>0.049217</v>
+        <v>0.049535</v>
       </c>
       <c r="G4" t="n">
-        <v>0.227718</v>
+        <v>0.228795</v>
       </c>
       <c r="H4" t="n">
-        <v>0.274223</v>
+        <v>0.275792</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001073</v>
+        <v>0.001081</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005162</v>
+        <v>0.005206</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00366</v>
+        <v>0.003693</v>
       </c>
       <c r="G5" t="n">
-        <v>0.016933</v>
+        <v>0.017057</v>
       </c>
       <c r="H5" t="n">
-        <v>0.020392</v>
+        <v>0.020562</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,19 +465,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="C2" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02454</v>
+        <v>0.023161</v>
       </c>
       <c r="E2" t="n">
-        <v>0.135901</v>
+        <v>0.136611</v>
       </c>
       <c r="F2" t="n">
-        <v>0.061784</v>
+        <v>0.061712</v>
       </c>
       <c r="G2" t="n">
         <v>0.672434</v>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="C3" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D3" t="n">
-        <v>0.013417</v>
+        <v>0.013454</v>
       </c>
       <c r="E3" t="n">
-        <v>0.064624</v>
+        <v>0.06896099999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.045842</v>
+        <v>0.048184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.211738</v>
+        <v>0.229919</v>
       </c>
       <c r="H3" t="n">
-        <v>0.25523</v>
+        <v>0.260714</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="C4" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014498</v>
+        <v>0.014318</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06983</v>
+        <v>0.073389</v>
       </c>
       <c r="F4" t="n">
-        <v>0.049535</v>
+        <v>0.051278</v>
       </c>
       <c r="G4" t="n">
-        <v>0.228795</v>
+        <v>0.244684</v>
       </c>
       <c r="H4" t="n">
-        <v>0.275792</v>
+        <v>0.277456</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.001081</v>
+        <v>0.000864</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005206</v>
+        <v>0.004428</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003693</v>
+        <v>0.003094</v>
       </c>
       <c r="G5" t="n">
-        <v>0.017057</v>
+        <v>0.014765</v>
       </c>
       <c r="H5" t="n">
-        <v>0.020562</v>
+        <v>0.016742</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,22 +465,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="C2" t="n">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023161</v>
+        <v>0.023407</v>
       </c>
       <c r="E2" t="n">
-        <v>0.136611</v>
+        <v>0.130427</v>
       </c>
       <c r="F2" t="n">
-        <v>0.061712</v>
+        <v>0.060827</v>
       </c>
       <c r="G2" t="n">
-        <v>0.672434</v>
+        <v>0.634074</v>
       </c>
       <c r="H2" t="n">
         <v>0.711338</v>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="C3" t="n">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D3" t="n">
-        <v>0.013454</v>
+        <v>0.01347</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06896099999999999</v>
+        <v>0.069212</v>
       </c>
       <c r="F3" t="n">
-        <v>0.048184</v>
+        <v>0.048049</v>
       </c>
       <c r="G3" t="n">
-        <v>0.229919</v>
+        <v>0.229012</v>
       </c>
       <c r="H3" t="n">
-        <v>0.260714</v>
+        <v>0.258875</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="C4" t="n">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014318</v>
+        <v>0.014324</v>
       </c>
       <c r="E4" t="n">
-        <v>0.073389</v>
+        <v>0.073604</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051278</v>
+        <v>0.051098</v>
       </c>
       <c r="G4" t="n">
-        <v>0.244684</v>
+        <v>0.243544</v>
       </c>
       <c r="H4" t="n">
-        <v>0.277456</v>
+        <v>0.275302</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.000864</v>
+        <v>0.000854</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004428</v>
+        <v>0.004392</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003094</v>
+        <v>0.003049</v>
       </c>
       <c r="G5" t="n">
-        <v>0.014765</v>
+        <v>0.014532</v>
       </c>
       <c r="H5" t="n">
-        <v>0.016742</v>
+        <v>0.016427</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -468,19 +468,19 @@
         <v>674</v>
       </c>
       <c r="C2" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023407</v>
+        <v>0.02272</v>
       </c>
       <c r="E2" t="n">
-        <v>0.130427</v>
+        <v>0.125546</v>
       </c>
       <c r="F2" t="n">
         <v>0.060827</v>
       </c>
       <c r="G2" t="n">
-        <v>0.634074</v>
+        <v>0.620194</v>
       </c>
       <c r="H2" t="n">
         <v>0.711338</v>
@@ -496,22 +496,22 @@
         <v>674</v>
       </c>
       <c r="C3" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01347</v>
+        <v>0.013478</v>
       </c>
       <c r="E3" t="n">
-        <v>0.069212</v>
+        <v>0.068773</v>
       </c>
       <c r="F3" t="n">
-        <v>0.048049</v>
+        <v>0.04813</v>
       </c>
       <c r="G3" t="n">
-        <v>0.229012</v>
+        <v>0.227431</v>
       </c>
       <c r="H3" t="n">
-        <v>0.258875</v>
+        <v>0.257426</v>
       </c>
     </row>
     <row r="4">
@@ -524,22 +524,22 @@
         <v>674</v>
       </c>
       <c r="C4" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014324</v>
+        <v>0.014296</v>
       </c>
       <c r="E4" t="n">
-        <v>0.073604</v>
+        <v>0.07294399999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051098</v>
+        <v>0.051049</v>
       </c>
       <c r="G4" t="n">
-        <v>0.243544</v>
+        <v>0.241226</v>
       </c>
       <c r="H4" t="n">
-        <v>0.275302</v>
+        <v>0.273041</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.000854</v>
+        <v>0.000818</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004392</v>
+        <v>0.004171</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003049</v>
+        <v>0.002919</v>
       </c>
       <c r="G5" t="n">
-        <v>0.014532</v>
+        <v>0.013795</v>
       </c>
       <c r="H5" t="n">
-        <v>0.016427</v>
+        <v>0.015615</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -499,19 +499,19 @@
         <v>368</v>
       </c>
       <c r="D3" t="n">
-        <v>0.013478</v>
+        <v>0.013562</v>
       </c>
       <c r="E3" t="n">
-        <v>0.068773</v>
+        <v>0.069107</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04813</v>
+        <v>0.04833</v>
       </c>
       <c r="G3" t="n">
-        <v>0.227431</v>
+        <v>0.225764</v>
       </c>
       <c r="H3" t="n">
-        <v>0.257426</v>
+        <v>0.258349</v>
       </c>
     </row>
     <row r="4">
@@ -527,19 +527,19 @@
         <v>368</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014296</v>
+        <v>0.014355</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07294399999999999</v>
+        <v>0.073148</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051049</v>
+        <v>0.051156</v>
       </c>
       <c r="G4" t="n">
-        <v>0.241226</v>
+        <v>0.238965</v>
       </c>
       <c r="H4" t="n">
-        <v>0.273041</v>
+        <v>0.273454</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.000818</v>
+        <v>0.000793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004171</v>
+        <v>0.004041</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002919</v>
+        <v>0.002826</v>
       </c>
       <c r="G5" t="n">
-        <v>0.013795</v>
+        <v>0.013201</v>
       </c>
       <c r="H5" t="n">
-        <v>0.015615</v>
+        <v>0.015105</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,19 +465,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C2" t="n">
         <v>368</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02272</v>
+        <v>0.022803</v>
       </c>
       <c r="E2" t="n">
-        <v>0.125546</v>
+        <v>0.125749</v>
       </c>
       <c r="F2" t="n">
-        <v>0.060827</v>
+        <v>0.060882</v>
       </c>
       <c r="G2" t="n">
         <v>0.620194</v>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C3" t="n">
         <v>368</v>
       </c>
       <c r="D3" t="n">
-        <v>0.013562</v>
+        <v>0.01369</v>
       </c>
       <c r="E3" t="n">
-        <v>0.069107</v>
+        <v>0.06944500000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04833</v>
+        <v>0.048376</v>
       </c>
       <c r="G3" t="n">
-        <v>0.225764</v>
+        <v>0.225119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.258349</v>
+        <v>0.258728</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C4" t="n">
         <v>368</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014355</v>
+        <v>0.014478</v>
       </c>
       <c r="E4" t="n">
-        <v>0.073148</v>
+        <v>0.073444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051156</v>
+        <v>0.051161</v>
       </c>
       <c r="G4" t="n">
-        <v>0.238965</v>
+        <v>0.238082</v>
       </c>
       <c r="H4" t="n">
-        <v>0.273454</v>
+        <v>0.273627</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.000793</v>
+        <v>0.000788</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004041</v>
+        <v>0.003999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002826</v>
+        <v>0.002785</v>
       </c>
       <c r="G5" t="n">
-        <v>0.013201</v>
+        <v>0.012963</v>
       </c>
       <c r="H5" t="n">
-        <v>0.015105</v>
+        <v>0.014899</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,19 +465,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="C2" t="n">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="D2" t="n">
-        <v>0.022803</v>
+        <v>0.02764</v>
       </c>
       <c r="E2" t="n">
-        <v>0.125749</v>
+        <v>0.117607</v>
       </c>
       <c r="F2" t="n">
-        <v>0.060882</v>
+        <v>0.059367</v>
       </c>
       <c r="G2" t="n">
         <v>0.620194</v>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="C3" t="n">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01369</v>
+        <v>0.018857</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06944500000000001</v>
+        <v>0.065346</v>
       </c>
       <c r="F3" t="n">
-        <v>0.048376</v>
+        <v>0.048505</v>
       </c>
       <c r="G3" t="n">
-        <v>0.225119</v>
+        <v>0.234258</v>
       </c>
       <c r="H3" t="n">
-        <v>0.258728</v>
+        <v>0.293574</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="C4" t="n">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014478</v>
+        <v>0.019826</v>
       </c>
       <c r="E4" t="n">
-        <v>0.073444</v>
+        <v>0.068705</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051161</v>
+        <v>0.050998</v>
       </c>
       <c r="G4" t="n">
-        <v>0.238082</v>
+        <v>0.246299</v>
       </c>
       <c r="H4" t="n">
-        <v>0.273627</v>
+        <v>0.308663</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.000788</v>
+        <v>0.000969</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003999</v>
+        <v>0.003359</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002785</v>
+        <v>0.002493</v>
       </c>
       <c r="G5" t="n">
-        <v>0.012963</v>
+        <v>0.012041</v>
       </c>
       <c r="H5" t="n">
-        <v>0.014899</v>
+        <v>0.015089</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -502,16 +502,16 @@
         <v>0.018857</v>
       </c>
       <c r="E3" t="n">
-        <v>0.065346</v>
+        <v>0.065344</v>
       </c>
       <c r="F3" t="n">
-        <v>0.048505</v>
+        <v>0.0485</v>
       </c>
       <c r="G3" t="n">
-        <v>0.234258</v>
+        <v>0.234331</v>
       </c>
       <c r="H3" t="n">
-        <v>0.293574</v>
+        <v>0.293547</v>
       </c>
     </row>
     <row r="4">
@@ -527,19 +527,19 @@
         <v>398</v>
       </c>
       <c r="D4" t="n">
-        <v>0.019826</v>
+        <v>0.01983</v>
       </c>
       <c r="E4" t="n">
-        <v>0.068705</v>
+        <v>0.068717</v>
       </c>
       <c r="F4" t="n">
-        <v>0.050998</v>
+        <v>0.051004</v>
       </c>
       <c r="G4" t="n">
-        <v>0.246299</v>
+        <v>0.246428</v>
       </c>
       <c r="H4" t="n">
-        <v>0.308663</v>
+        <v>0.3087</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.000969</v>
+        <v>0.000973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003359</v>
+        <v>0.003373</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002493</v>
+        <v>0.002504</v>
       </c>
       <c r="G5" t="n">
-        <v>0.012041</v>
+        <v>0.012097</v>
       </c>
       <c r="H5" t="n">
-        <v>0.015089</v>
+        <v>0.015153</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,19 +465,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C2" t="n">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02764</v>
+        <v>0.027314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.117607</v>
+        <v>0.11606</v>
       </c>
       <c r="F2" t="n">
-        <v>0.059367</v>
+        <v>0.058745</v>
       </c>
       <c r="G2" t="n">
         <v>0.620194</v>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C3" t="n">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D3" t="n">
-        <v>0.018857</v>
+        <v>0.018568</v>
       </c>
       <c r="E3" t="n">
-        <v>0.065344</v>
+        <v>0.064884</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0485</v>
+        <v>0.048185</v>
       </c>
       <c r="G3" t="n">
-        <v>0.234331</v>
+        <v>0.237935</v>
       </c>
       <c r="H3" t="n">
-        <v>0.293547</v>
+        <v>0.297704</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C4" t="n">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01983</v>
+        <v>0.019497</v>
       </c>
       <c r="E4" t="n">
-        <v>0.068717</v>
+        <v>0.06813</v>
       </c>
       <c r="F4" t="n">
-        <v>0.051004</v>
+        <v>0.050595</v>
       </c>
       <c r="G4" t="n">
-        <v>0.246428</v>
+        <v>0.249837</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3087</v>
+        <v>0.312595</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.000973</v>
+        <v>0.000929</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003373</v>
+        <v>0.003246</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002504</v>
+        <v>0.00241</v>
       </c>
       <c r="G5" t="n">
-        <v>0.012097</v>
+        <v>0.011902</v>
       </c>
       <c r="H5" t="n">
-        <v>0.015153</v>
+        <v>0.014891</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -471,13 +471,13 @@
         <v>394</v>
       </c>
       <c r="D2" t="n">
-        <v>0.027314</v>
+        <v>0.027338</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11606</v>
+        <v>0.116067</v>
       </c>
       <c r="F2" t="n">
-        <v>0.058745</v>
+        <v>0.058836</v>
       </c>
       <c r="G2" t="n">
         <v>0.620194</v>
@@ -499,19 +499,19 @@
         <v>394</v>
       </c>
       <c r="D3" t="n">
-        <v>0.018568</v>
+        <v>0.018596</v>
       </c>
       <c r="E3" t="n">
-        <v>0.064884</v>
+        <v>0.064919</v>
       </c>
       <c r="F3" t="n">
-        <v>0.048185</v>
+        <v>0.048499</v>
       </c>
       <c r="G3" t="n">
-        <v>0.237935</v>
+        <v>0.23821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.297704</v>
+        <v>0.297977</v>
       </c>
     </row>
     <row r="4">
@@ -527,19 +527,19 @@
         <v>394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.019497</v>
+        <v>0.019526</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06813</v>
+        <v>0.068165</v>
       </c>
       <c r="F4" t="n">
-        <v>0.050595</v>
+        <v>0.050924</v>
       </c>
       <c r="G4" t="n">
-        <v>0.249837</v>
+        <v>0.250119</v>
       </c>
       <c r="H4" t="n">
-        <v>0.312595</v>
+        <v>0.312875</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.000929</v>
+        <v>0.0009300000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0.003246</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00241</v>
+        <v>0.002425</v>
       </c>
       <c r="G5" t="n">
-        <v>0.011902</v>
+        <v>0.011909</v>
       </c>
       <c r="H5" t="n">
-        <v>0.014891</v>
+        <v>0.014898</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/distribution_stats.xlsx
+++ b/vignettes/vignette-2/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="C2" t="n">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D2" t="n">
-        <v>0.027338</v>
+        <v>0.026645</v>
       </c>
       <c r="E2" t="n">
-        <v>0.116067</v>
+        <v>0.112082</v>
       </c>
       <c r="F2" t="n">
-        <v>0.058836</v>
+        <v>0.058745</v>
       </c>
       <c r="G2" t="n">
-        <v>0.620194</v>
+        <v>0.6049369999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.711338</v>
+        <v>0.672434</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="C3" t="n">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D3" t="n">
-        <v>0.018596</v>
+        <v>0.018754</v>
       </c>
       <c r="E3" t="n">
-        <v>0.064919</v>
+        <v>0.065386</v>
       </c>
       <c r="F3" t="n">
-        <v>0.048499</v>
+        <v>0.04819</v>
       </c>
       <c r="G3" t="n">
-        <v>0.23821</v>
+        <v>0.245853</v>
       </c>
       <c r="H3" t="n">
-        <v>0.297977</v>
+        <v>0.304954</v>
       </c>
     </row>
     <row r="4">
@@ -521,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="C4" t="n">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D4" t="n">
-        <v>0.019526</v>
+        <v>0.019705</v>
       </c>
       <c r="E4" t="n">
-        <v>0.068165</v>
+        <v>0.068699</v>
       </c>
       <c r="F4" t="n">
-        <v>0.050924</v>
+        <v>0.050632</v>
       </c>
       <c r="G4" t="n">
-        <v>0.250119</v>
+        <v>0.258309</v>
       </c>
       <c r="H4" t="n">
-        <v>0.312875</v>
+        <v>0.320405</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.0009300000000000001</v>
+        <v>0.000951</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003246</v>
+        <v>0.003313</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002425</v>
+        <v>0.002442</v>
       </c>
       <c r="G5" t="n">
-        <v>0.011909</v>
+        <v>0.012456</v>
       </c>
       <c r="H5" t="n">
-        <v>0.014898</v>
+        <v>0.015451</v>
       </c>
     </row>
   </sheetData>
